--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62427.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62427.xlsx
@@ -614,7 +614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,27 +699,18 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
+      <c r="J4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="C5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -727,7 +718,16 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -735,7 +735,23 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="n">
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="n">
         <v>1</v>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62427.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62427.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cailel</t>
+          <t>C lalali llule</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CYPTEV</t>
+          <t>HLALETLE N I</t>
         </is>
       </c>
     </row>
